--- a/app/zen_rules/bank_Individual_Eligibility_Matrix.xlsx
+++ b/app/zen_rules/bank_Individual_Eligibility_Matrix.xlsx
@@ -157,10 +157,10 @@
     <t>Self Employed-ITR Not Filed</t>
   </si>
   <si>
-    <t>Business ITR Years</t>
-  </si>
-  <si>
-    <t>Business Proof</t>
+    <t>Self-employed-Business ITR Years</t>
+  </si>
+  <si>
+    <t>Self-employed-Business Proof</t>
   </si>
   <si>
     <t>Self Employed-Propreitorship</t>

--- a/app/zen_rules/bank_Individual_Eligibility_Matrix.xlsx
+++ b/app/zen_rules/bank_Individual_Eligibility_Matrix.xlsx
@@ -318,7 +318,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,6 +329,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -365,10 +371,10 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -922,7 +928,7 @@
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
@@ -1101,7 +1107,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
@@ -1280,7 +1286,7 @@
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1465,7 @@
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>84</v>
       </c>
@@ -1638,7 +1644,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>88</v>
       </c>
@@ -1817,7 +1823,7 @@
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>92</v>
       </c>
@@ -1996,7 +2002,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>95</v>
       </c>
@@ -2175,7 +2181,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>97</v>
       </c>

--- a/app/zen_rules/bank_Individual_Eligibility_Matrix.xlsx
+++ b/app/zen_rules/bank_Individual_Eligibility_Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="100">
   <si>
     <t>Bank Name</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>&gt;= 726</t>
+  </si>
+  <si>
+    <t>condition</t>
   </si>
   <si>
     <t>Current + Prev &gt;= 600000</t>
@@ -318,19 +321,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -366,15 +363,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -688,65 +682,65 @@
   <dimension ref="A1:BG9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="4" width="27.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="4" width="34.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="4" width="27.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="4" width="27.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="4" width="50.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="4" width="46.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="4" width="44.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="4" width="51.005" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="4" width="26.005" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="4" width="19.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="4" width="24.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="4" width="23.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="4" width="27.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="4" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="4" width="24.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="4" width="24.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="4" width="31.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="4" width="31.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="4" width="30.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="4" width="22.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="4" width="65.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="4" width="58.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="4" width="64.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="4" width="30.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="4" width="30.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="4" width="27.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="4" width="20.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="4" width="24.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="47" max="47" style="4" width="31.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="48" max="48" style="4" width="24.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="49" max="49" style="4" width="26.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="50" max="50" style="4" width="30.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="51" max="51" style="4" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="52" max="52" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="53" max="53" style="4" width="23.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="54" max="54" style="4" width="27.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="55" max="55" style="4" width="27.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="56" max="56" style="4" width="27.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="57" max="57" style="4" width="26.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="58" max="58" style="4" width="26.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="59" max="59" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="3" width="27.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="3" width="34.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="3" width="27.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="3" width="27.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="3" width="50.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="3" width="46.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="3" width="44.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="3" width="51.005" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="3" width="26.005" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="3" width="19.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="3" width="24.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="3" width="23.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="3" width="27.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="3" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="3" width="24.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="3" width="24.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="3" width="31.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="3" width="31.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="3" width="30.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="3" width="22.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="3" width="65.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="40" max="40" style="3" width="58.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="41" max="41" style="3" width="64.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="3" width="30.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="3" width="30.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="3" width="27.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="3" width="20.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="3" width="24.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="47" max="47" style="3" width="31.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="48" max="48" style="3" width="24.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="49" max="49" style="3" width="26.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="50" max="50" style="3" width="30.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="51" max="51" style="3" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="52" max="52" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="53" max="53" style="3" width="23.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="54" max="54" style="3" width="27.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="55" max="55" style="3" width="27.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="56" max="56" style="3" width="27.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="57" max="57" style="3" width="26.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="58" max="58" style="3" width="26.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="59" max="59" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -971,7 +965,7 @@
       <c r="N2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
         <v>21</v>
       </c>
       <c r="P2" s="1" t="s">
@@ -1150,7 +1144,7 @@
       <c r="N3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="2">
         <v>21</v>
       </c>
       <c r="P3" s="1" t="s">
@@ -1329,7 +1323,7 @@
       <c r="N4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <v>21</v>
       </c>
       <c r="P4" s="1" t="s">
@@ -1508,7 +1502,7 @@
       <c r="N5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <v>21</v>
       </c>
       <c r="P5" s="1" t="s">
@@ -1593,10 +1587,10 @@
         <v>70</v>
       </c>
       <c r="AQ5" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="AR5" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AS5" s="1" t="s">
         <v>63</v>
@@ -1646,13 +1640,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>62</v>
@@ -1676,7 +1670,7 @@
         <v>63</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>65</v>
@@ -1687,7 +1681,7 @@
       <c r="N6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="2">
         <v>21</v>
       </c>
       <c r="P6" s="1" t="s">
@@ -1825,10 +1819,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>61</v>
@@ -1866,7 +1860,7 @@
       <c r="N7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="2">
         <v>21</v>
       </c>
       <c r="P7" s="1" t="s">
@@ -1927,7 +1921,7 @@
         <v>69</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AJ7" s="1" t="s">
         <v>62</v>
@@ -2004,10 +1998,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>61</v>
@@ -2045,7 +2039,7 @@
       <c r="N8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="2">
         <v>21</v>
       </c>
       <c r="P8" s="1" t="s">
@@ -2106,7 +2100,7 @@
         <v>69</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AJ8" s="1" t="s">
         <v>62</v>
@@ -2183,10 +2177,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>61</v>
@@ -2224,7 +2218,7 @@
       <c r="N9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="2">
         <v>21</v>
       </c>
       <c r="P9" s="1" t="s">
@@ -2285,7 +2279,7 @@
         <v>69</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AJ9" s="1" t="s">
         <v>62</v>
